--- a/artfynd/A 48832-2024 artfynd.xlsx
+++ b/artfynd/A 48832-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136211426</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136211427</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136211422</v>
       </c>
       <c r="B4" t="n">
-        <v>97405</v>
+        <v>97406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136211425</v>
       </c>
       <c r="B5" t="n">
-        <v>58685</v>
+        <v>58686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136211429</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136211430</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136211431</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136211424</v>
       </c>
       <c r="B9" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136211423</v>
       </c>
       <c r="B10" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48832-2024 artfynd.xlsx
+++ b/artfynd/A 48832-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136211426</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136211427</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136211422</v>
       </c>
       <c r="B4" t="n">
-        <v>97406</v>
+        <v>97412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136211425</v>
       </c>
       <c r="B5" t="n">
-        <v>58686</v>
+        <v>58690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136211429</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136211430</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136211431</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136211424</v>
       </c>
       <c r="B9" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136211423</v>
       </c>
       <c r="B10" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48832-2024 artfynd.xlsx
+++ b/artfynd/A 48832-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136211426</v>
       </c>
       <c r="B2" t="n">
-        <v>99300</v>
+        <v>99301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136211427</v>
       </c>
       <c r="B3" t="n">
-        <v>99300</v>
+        <v>99301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136211422</v>
       </c>
       <c r="B4" t="n">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136211425</v>
       </c>
       <c r="B5" t="n">
-        <v>58690</v>
+        <v>58691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136211429</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136211430</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136211431</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136211424</v>
       </c>
       <c r="B9" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136211423</v>
       </c>
       <c r="B10" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
